--- a/data/trans_camb/P19C09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,17</t>
+          <t>-0,44; 3,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,85</t>
+          <t>0,55; 5,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,18</t>
+          <t>0,03; 4,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,99</t>
+          <t>-0,74; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,89</t>
+          <t>0,15; 2,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,03</t>
+          <t>0,36; 3,37</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 900,84</t>
+          <t>-45,72; 1132,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 1584,16</t>
+          <t>1,79; 1436,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 893,4</t>
+          <t>-17,5; 909,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 749,25</t>
+          <t>-54,31; 623,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 392,38</t>
+          <t>3,2; 449,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 423,49</t>
+          <t>14,72; 506,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,55</t>
+          <t>-1,91; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,0</t>
+          <t>-0,92; 3,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,19</t>
+          <t>-1,02; 3,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,03</t>
+          <t>-1,19; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,78</t>
+          <t>-0,81; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,55</t>
+          <t>-0,46; 2,4</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,74; 158,71</t>
+          <t>-67,25; 149,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 250,45</t>
+          <t>-34,9; 285,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 213,63</t>
+          <t>-32,3; 207,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 211,0</t>
+          <t>-37,82; 216,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 112,97</t>
+          <t>-30,07; 122,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 158,89</t>
+          <t>-17,65; 158,41</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,47</t>
+          <t>-3,11; 0,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,33</t>
+          <t>-0,97; 3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,65</t>
+          <t>-0,88; 2,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,0</t>
+          <t>-1,36; 1,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,22</t>
+          <t>-1,34; 1,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,0</t>
+          <t>-0,58; 2,0</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 52,64</t>
+          <t>-85,04; 62,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 203,06</t>
+          <t>-31,76; 220,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 247,16</t>
+          <t>-41,07; 273,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 192,29</t>
+          <t>-53,96; 200,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 90,03</t>
+          <t>-50,03; 78,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 138,94</t>
+          <t>-23,14; 132,32</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,03</t>
+          <t>-2,43; 1,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,38</t>
+          <t>-1,63; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,41</t>
+          <t>-3,87; 0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,16</t>
+          <t>-3,07; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,32</t>
+          <t>-2,39; 0,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,21</t>
+          <t>-1,63; 1,08</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 245,27</t>
+          <t>-86,27; 204,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,61; 369,0</t>
+          <t>-69,14; 320,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,53; 29,68</t>
+          <t>-79,34; 33,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 55,26</t>
+          <t>-69,85; 68,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 23,89</t>
+          <t>-72,19; 19,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,49; 65,83</t>
+          <t>-49,85; 66,4</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,47</t>
+          <t>-4,34; 0,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,68</t>
+          <t>-4,55; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -0,6</t>
+          <t>-6,58; -0,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 1,16</t>
+          <t>-5,32; 0,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,82</t>
+          <t>-4,79; -0,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,14</t>
+          <t>-4,17; -0,01</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 40,25</t>
+          <t>-85,38; 59,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,59; 53,35</t>
+          <t>-84,17; 39,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,18; -6,94</t>
+          <t>-84,03; -15,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,84; 34,68</t>
+          <t>-69,33; 31,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,77; -16,12</t>
+          <t>-77,74; -20,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 4,54</t>
+          <t>-66,68; 3,84</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,38</t>
+          <t>-4,02; 3,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,81</t>
+          <t>-5,82; 0,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,51</t>
+          <t>-7,23; -0,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,52</t>
+          <t>-7,54; -0,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,74</t>
+          <t>-4,76; 0,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,89</t>
+          <t>-5,38; -0,61</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,06; 148,82</t>
+          <t>-69,68; 170,79</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,03; 58,95</t>
+          <t>-87,79; 31,33</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,52; -0,58</t>
+          <t>-85,67; -3,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-88,78; -3,25</t>
+          <t>-89,22; -4,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 27,19</t>
+          <t>-71,46; 18,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,49; -17,85</t>
+          <t>-80,56; -10,45</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -4,27</t>
+          <t>-14,71; -4,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 2,35</t>
+          <t>-10,64; 2,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,69</t>
+          <t>-4,49; 3,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,68</t>
+          <t>-6,12; 1,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -0,46</t>
+          <t>-6,93; -0,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,67</t>
+          <t>-6,85; 0,3</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -32,62</t>
+          <t>-100,0; -26,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 54,87</t>
+          <t>-77,92; 41,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 138,78</t>
+          <t>-64,74; 146,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-88,24; 105,6</t>
+          <t>-88,13; 125,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,56; -7,53</t>
+          <t>-77,53; -7,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 17,86</t>
+          <t>-74,15; 15,46</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; -0,13</t>
+          <t>-1,75; -0,09</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,15</t>
+          <t>-0,71; 1,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,59</t>
+          <t>-1,27; 0,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,38</t>
+          <t>-1,37; 0,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,04</t>
+          <t>-1,22; 0,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,46</t>
+          <t>-0,71; 0,53</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-57,34; -4,59</t>
+          <t>-56,35; -2,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 51,5</t>
+          <t>-23,79; 59,45</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 22,96</t>
+          <t>-34,6; 20,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 14,71</t>
+          <t>-39,36; 16,09</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,9; -0,88</t>
+          <t>-38,31; 0,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 17,95</t>
+          <t>-22,34; 21,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,07</t>
+          <t>-0,45; 2,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,01</t>
+          <t>0,49; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,24</t>
+          <t>-0,12; 4,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,95</t>
+          <t>-0,88; 2,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,87</t>
+          <t>0,18; 2,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,37</t>
+          <t>0,3; 3,2</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 1132,82</t>
+          <t>-48,3; 795,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 1436,54</t>
+          <t>-9,84; 1311,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 909,31</t>
+          <t>-18,24; 700,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 623,14</t>
+          <t>-49,09; 473,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 449,43</t>
+          <t>-1,65; 454,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 506,0</t>
+          <t>8,78; 524,23</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,53</t>
+          <t>-2,05; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,19</t>
+          <t>-1,1; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,11</t>
+          <t>-0,81; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,2</t>
+          <t>-1,09; 3,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,94</t>
+          <t>-0,97; 1,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,4</t>
+          <t>-0,47; 2,43</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,25; 149,74</t>
+          <t>-66,46; 135,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 285,98</t>
+          <t>-39,08; 238,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 207,79</t>
+          <t>-26,76; 253,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 216,49</t>
+          <t>-36,3; 225,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 122,44</t>
+          <t>-34,81; 112,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 158,41</t>
+          <t>-18,24; 147,85</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,31</t>
+          <t>-3,17; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,04</t>
+          <t>-1,3; 3,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,77</t>
+          <t>-0,92; 2,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,99</t>
+          <t>-1,37; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,19</t>
+          <t>-1,29; 1,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,0</t>
+          <t>-0,62; 2,16</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,04; 62,16</t>
+          <t>-86,19; 52,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 220,85</t>
+          <t>-42,34; 210,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 273,51</t>
+          <t>-42,8; 265,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 200,19</t>
+          <t>-54,16; 193,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 78,63</t>
+          <t>-48,3; 84,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 132,32</t>
+          <t>-22,67; 147,87</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,01</t>
+          <t>-2,5; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,07</t>
+          <t>-1,67; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,47</t>
+          <t>-3,92; 0,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,35</t>
+          <t>-3,29; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,31</t>
+          <t>-2,48; 0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,08</t>
+          <t>-1,9; 1,02</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,27; 204,68</t>
+          <t>-85,42; 205,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 320,24</t>
+          <t>-60,43; 316,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,34; 33,69</t>
+          <t>-81,16; 30,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,85; 68,43</t>
+          <t>-69,12; 78,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,19; 19,43</t>
+          <t>-73,23; 21,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 66,4</t>
+          <t>-55,76; 62,31</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,9</t>
+          <t>-4,45; 0,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,68</t>
+          <t>-4,59; 0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -0,88</t>
+          <t>-6,62; -0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,94</t>
+          <t>-5,4; 0,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -0,88</t>
+          <t>-4,71; -0,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,01</t>
+          <t>-4,33; 0,18</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-85,38; 59,6</t>
+          <t>-85,49; 39,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,17; 39,6</t>
+          <t>-81,99; 62,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,03; -15,15</t>
+          <t>-86,1; -8,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 31,41</t>
+          <t>-68,6; 23,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,74; -20,29</t>
+          <t>-78,18; -14,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 3,84</t>
+          <t>-69,2; 6,34</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,97</t>
+          <t>-3,7; 3,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,46</t>
+          <t>-5,69; 0,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,4</t>
+          <t>-7,43; -0,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,54; -0,63</t>
+          <t>-7,15; -0,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,43</t>
+          <t>-4,67; 0,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,61</t>
+          <t>-5,44; -0,95</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,68; 170,79</t>
+          <t>-64,94; 164,88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-87,79; 31,33</t>
+          <t>-86,99; 70,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-85,67; -3,45</t>
+          <t>-86,11; 1,71</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-89,22; -4,79</t>
+          <t>-87,73; -10,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 18,36</t>
+          <t>-71,01; 4,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,56; -10,45</t>
+          <t>-80,25; -19,72</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -4,31</t>
+          <t>-14,94; -4,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 2,09</t>
+          <t>-9,95; 2,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,57</t>
+          <t>-4,35; 3,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,53</t>
+          <t>-6,12; 1,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -0,63</t>
+          <t>-6,93; -0,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,3</t>
+          <t>-6,29; 0,64</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,12</t>
+          <t>-100,0; -48,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 41,89</t>
+          <t>-74,52; 55,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 146,37</t>
+          <t>-62,79; 141,73</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 125,89</t>
+          <t>-88,83; 90,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-77,53; -7,66</t>
+          <t>-76,99; -0,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 15,46</t>
+          <t>-72,77; 19,61</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,09</t>
+          <t>-1,7; -0,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,29</t>
+          <t>-0,74; 1,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,54</t>
+          <t>-1,23; 0,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,42</t>
+          <t>-1,42; 0,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,01</t>
+          <t>-1,32; -0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,53</t>
+          <t>-0,81; 0,5</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -2,49</t>
+          <t>-53,94; 0,68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 59,45</t>
+          <t>-24,78; 53,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 20,59</t>
+          <t>-33,47; 23,9</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 16,09</t>
+          <t>-38,51; 16,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 0,43</t>
+          <t>-39,49; -0,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 21,09</t>
+          <t>-25,28; 19,99</t>
         </is>
       </c>
     </row>
